--- a/data/trans_dic/P13A_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P13A_1_R-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses)</t>
+          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,11</t>
+          <t>0,03; 1,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,91</t>
+          <t>1,69; 4,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,44</t>
+          <t>0,93; 2,42</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,84</t>
+          <t>1,84; 4,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,3</t>
+          <t>0,95; 2,35</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,55</t>
+          <t>0,3; 2,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,32; 12,33</t>
+          <t>4,45; 13,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,15</t>
+          <t>0,79; 4,01</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,08</t>
+          <t>0,68; 2,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,5</t>
+          <t>1,75; 5,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,29</t>
+          <t>1,69; 3,25</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,32</t>
+          <t>1,18; 4,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 8,41</t>
+          <t>4,2; 8,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,22</t>
+          <t>3,4; 6,39</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,34; 3,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,24</t>
+          <t>1,5; 3,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,82</t>
+          <t>1,27; 2,7</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,54</t>
+          <t>0,77; 1,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,21; 4,8</t>
+          <t>3,18; 4,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,03</t>
+          <t>2,16; 3,04</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses)</t>
+          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>164; 5559</t>
+          <t>163; 5689</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7780; 21954</t>
+          <t>7561; 20988</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8958; 23191</t>
+          <t>8874; 22944</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5171</t>
+          <t>0; 6079</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7462; 18461</t>
+          <t>7014; 17901</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7578; 19181</t>
+          <t>7944; 19582</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1496; 17051</t>
+          <t>2035; 17282</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7179; 20504</t>
+          <t>7408; 22266</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7665; 34580</t>
+          <t>6567; 33433</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7237; 21491</t>
+          <t>7049; 22125</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18114; 53623</t>
+          <t>17072; 52900</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34708; 66153</t>
+          <t>33934; 65314</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5265; 20421</t>
+          <t>5600; 20807</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34815; 70354</t>
+          <t>35149; 70596</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45964; 81394</t>
+          <t>44490; 83683</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 8644</t>
+          <t>829; 8343</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11447; 24524</t>
+          <t>11352; 23973</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13234; 28187</t>
+          <t>12688; 26964</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>24882; 51906</t>
+          <t>26034; 52623</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>114517; 171269</t>
+          <t>113275; 169131</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>148670; 210216</t>
+          <t>149751; 211009</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P13A_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P13A_1_R-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,13</t>
+          <t>0,11; 1,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,7</t>
+          <t>1,74; 4,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,42</t>
+          <t>1,05; 2,58</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,69</t>
+          <t>1,77; 4,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,35</t>
+          <t>0,87; 2,2</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,59</t>
+          <t>0,84; 3,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,45; 13,39</t>
+          <t>4,16; 12,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,01</t>
+          <t>2,16; 5,18</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,14</t>
+          <t>0,64; 1,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,42</t>
+          <t>3,78; 6,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,25</t>
+          <t>2,2; 3,64</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,4</t>
+          <t>0,98; 3,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,44</t>
+          <t>4,9; 8,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,39</t>
+          <t>3,59; 5,75</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,47</t>
+          <t>0,34; 3,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,16</t>
+          <t>1,38; 3,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,7</t>
+          <t>1,33; 2,77</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,56</t>
+          <t>0,85; 1,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,74</t>
+          <t>3,65; 4,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,04</t>
+          <t>2,39; 3,12</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>16799</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>163; 5689</t>
+          <t>582; 6973</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7561; 20988</t>
+          <t>8427; 22678</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8874; 22944</t>
+          <t>10882; 26655</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>13283</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6079</t>
+          <t>0; 5151</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7014; 17901</t>
+          <t>7457; 18987</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7944; 19582</t>
+          <t>7852; 19888</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20496</t>
+          <t>21554</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2035; 17282</t>
+          <t>3952; 16487</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7408; 22266</t>
+          <t>7785; 24170</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6567; 33433</t>
+          <t>14220; 34053</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38034</t>
+          <t>43468</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50772</t>
+          <t>56745</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7049; 22125</t>
+          <t>7170; 22108</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17072; 52900</t>
+          <t>32476; 56110</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33934; 65314</t>
+          <t>43753; 72337</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>51506</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60702</t>
+          <t>63375</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5600; 20807</t>
+          <t>5553; 20683</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>35149; 70596</t>
+          <t>40475; 66445</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44490; 83683</t>
+          <t>50000; 80035</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19578</t>
+          <t>21093</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>829; 8343</t>
+          <t>815; 9021</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11352; 23973</t>
+          <t>11618; 25611</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12688; 26964</t>
+          <t>14376; 29911</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>141533</t>
+          <t>152942</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178926</t>
+          <t>192850</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>26034; 52623</t>
+          <t>29063; 54418</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>113275; 169131</t>
+          <t>132213; 173161</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>149751; 211009</t>
+          <t>168372; 219773</t>
         </is>
       </c>
     </row>
